--- a/JsonConverter/ExcelFiles/TrainingFacilityData.xlsx
+++ b/JsonConverter/ExcelFiles/TrainingFacilityData.xlsx
@@ -19,162 +19,168 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한대 때리기 미안한 펀칭볼이다. 그래도 방심하다가 맞으면 꽤 아프다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오래 사용하다가는 골반이 틀어질 것 같은 느낌이 드는 러닝머신이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_streak_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainingDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좁은 휴식 공간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>낡은 휴식 공간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextLevelId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GoldCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>삐걱대는 러닝머신</x:t>
+  </x:si>
   <x:si>
     <x:t>cond_win_3</x:t>
   </x:si>
   <x:si>
-    <x:t>삐걱대는 러닝머신</x:t>
+    <x:t>cardio_01</x:t>
   </x:si>
   <x:si>
     <x:t>Cardio_01</x:t>
   </x:si>
   <x:si>
-    <x:t>cardio_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>cond_win_1</x:t>
   </x:si>
   <x:si>
-    <x:t>NextLevelId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GoldCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>낡은 휴식 공간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>좁은 휴식 공간</x:t>
+    <x:t>standing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing_Offense_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>standing_offense_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>standing_offense_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>standing_defense_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing_Defense_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingOffense</x:t>
   </x:si>
   <x:si>
     <x:t>낡고 보잘 것 없는 휴식 공간이다.</x:t>
   </x:si>
   <x:si>
-    <x:t>RequiredUnlockIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing_Strike_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>standing_strike_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>standing_strike_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing_Strike_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TrainingDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing_Atk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>standing_def_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing_Def_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing_Def</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MatchStamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_streak_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>한대 때리기 미안한 펀칭볼이다. 그래도 방심하다가 맞으면 꽤 아프다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오래 사용하다가는 골반이 틀어질 것 같은 느낌이 드는 러닝머신이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>def</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve"> </x:t>
+    <x:t>Standing_Offense_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Level</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rest_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rest_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>낡은 샌드백</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허름한 샌드백</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rest_02</x:t>
   </x:si>
   <x:si>
     <x:t>rest</x:t>
   </x:si>
   <x:si>
+    <x:t>Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
     <x:t>rest_01</x:t>
   </x:si>
   <x:si>
-    <x:t>고유 ID</x:t>
+    <x:t>찢어진 펀칭볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>cardio</x:t>
   </x:si>
   <x:si>
-    <x:t>낡은 샌드백</x:t>
-  </x:si>
-  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>rest_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rest_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>strike</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rest_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허름한 샌드백</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Level</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>찢어진 펀칭볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
+    <x:t>StandingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개선되었지만 여전히 좁고 불편한 휴식 공간이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainingStaminaPerSecond</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세월의 흔적이 느껴지는 낡은 샌드백이다.</x:t>
   </x:si>
   <x:si>
     <x:t>때리면 터질 것 같은 허름한 샌드백이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세월의 흔적이 느껴지는 낡은 샌드백이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TrainingStaminaPerSecond</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개선되었지만 여전히 좁고 불편한 휴식 공간이다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -928,144 +934,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:O35"/>
+  <x:dimension ref="A1:R35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="23.71484375" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="20.28515625" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="9.5703125" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="29.28515625" style="1" customWidth="1"/>
-    <x:col min="5" max="5" width="64.85546875" style="1" customWidth="1"/>
-    <x:col min="6" max="6" width="26.54296875" style="1" customWidth="1"/>
-    <x:col min="7" max="7" width="42.14453125" style="1" customWidth="1"/>
-    <x:col min="8" max="8" width="28.71484375" style="1" customWidth="1"/>
-    <x:col min="9" max="9" width="23" style="1" customWidth="1"/>
-    <x:col min="10" max="10" width="24.14453125" style="1" customWidth="1"/>
-    <x:col min="11" max="11" width="17.5703125" style="1" customWidth="1"/>
-    <x:col min="12" max="14" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="15" max="16384" width="12.54296875" style="1"/>
+    <x:col min="1" max="1" width="34.85546875" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="14.14453125" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="11.85546875" style="1" customWidth="1"/>
+    <x:col min="4" max="5" width="34.85546875" style="1" customWidth="1"/>
+    <x:col min="6" max="6" width="14.5703125" style="1" customWidth="1"/>
+    <x:col min="7" max="7" width="36.71484375" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="22.28515625" style="1" customWidth="1"/>
+    <x:col min="9" max="9" width="23.4296875" style="1" customWidth="1"/>
+    <x:col min="10" max="26" width="34.85546875" style="1" customWidth="1"/>
+    <x:col min="27" max="16384" width="12.54296875" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:14" ht="13.199999999999999">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:18" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="N2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R2" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:18" s="6" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="M3" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="N3" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O3" s="6" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="P3" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="Q3" s="6" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R3" s="6" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
+      <x:c r="A4" s="3" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J2" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="L2" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="M2" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N2" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:14" s="6" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H3" s="6" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I3" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J3" s="6" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K3" s="6" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L3" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M3" s="6" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="N3" s="6" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:14" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>30</x:v>
       </x:c>
       <x:c r="C4" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>500</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="J4" s="1">
         <x:v>10</x:v>
@@ -1082,34 +1109,46 @@
       <x:c r="N4" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O4" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P4" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q4" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R4" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C5" s="3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J5" s="1">
         <x:v>15</x:v>
@@ -1126,34 +1165,46 @@
       <x:c r="N5" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="O5" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P5" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q5" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R5" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="4">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F6" s="1">
         <x:v>200</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J6" s="4">
         <x:v>-5</x:v>
@@ -1162,24 +1213,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L6" s="1">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M6" s="1">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N6" s="1">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O6" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O6" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q6" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R6" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="4">
         <x:v>2</x:v>
@@ -1188,19 +1248,19 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F7" s="1">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I7" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J7" s="1">
         <x:v>-6</x:v>
@@ -1209,100 +1269,136 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L7" s="1">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M7" s="1">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N7" s="1">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:14" ht="15.75" customHeight="1">
+      <x:c r="O7" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C8" s="4">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>500</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J8" s="1">
         <x:v>-7</x:v>
       </x:c>
       <x:c r="K8" s="1">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="1">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M8" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N8" s="1">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:14" ht="15.75" customHeight="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" s="1">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="4">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>300</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I9" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J9" s="1">
         <x:v>-5</x:v>
       </x:c>
       <x:c r="K9" s="1">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L9" s="1">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M9" s="1">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N9" s="1">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R9" s="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>

--- a/JsonConverter/ExcelFiles/TrainingFacilityData.xlsx
+++ b/JsonConverter/ExcelFiles/TrainingFacilityData.xlsx
@@ -19,168 +19,171 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="54">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
+  <x:si>
+    <x:t>standing_defense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>한대 때리기 미안한 펀칭볼이다. 그래도 방심하다가 맞으면 꽤 아프다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오래 사용하다가는 골반이 틀어질 것 같은 느낌이 드는 러닝머신이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Level</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rest_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rest_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>낡은 샌드백</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rest_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허름한 샌드백</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rest_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stamina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cardio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>찢어진 펀칭볼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
   <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>한대 때리기 미안한 펀칭볼이다. 그래도 방심하다가 맞으면 꽤 아프다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오래 사용하다가는 골반이 틀어질 것 같은 느낌이 드는 러닝머신이다.</x:t>
+    <x:t>좁은 휴식 공간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GoldCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_win_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>삐걱대는 러닝머신</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextLevelId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cardio_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cardio_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>낡은 휴식 공간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cond_win_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing_Offense_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>standing_offense_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredUnlockIds</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingOffense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>낡고 보잘 것 없는 휴식 공간이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing_Defense_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standing_Offense_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>standing_offense_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>standing_defense_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WrestlingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TrainingStaminaPerSecond</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개선되었지만 여전히 좁고 불편한 휴식 공간이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StandingDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuDefense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JiuJitsuOffense</x:t>
   </x:si>
   <x:si>
     <x:t>cond_streak_3</x:t>
   </x:si>
   <x:si>
-    <x:t>StandingDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JiuJitsuDefense</x:t>
+    <x:t>StandingOffense</x:t>
   </x:si>
   <x:si>
     <x:t>TrainingDataId</x:t>
   </x:si>
   <x:si>
-    <x:t>좁은 휴식 공간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>낡은 휴식 공간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextLevelId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GoldCost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>삐걱대는 러닝머신</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_win_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cardio_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cardio_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cond_win_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>standing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing_Offense_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingDefense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>standing_offense_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredUnlockIds</x:t>
-  </x:si>
-  <x:si>
-    <x:t>standing_offense_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>standing_defense_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing_Defense_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WrestlingOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>낡고 보잘 것 없는 휴식 공간이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standing_Offense_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Level</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rest_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rest_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>낡은 샌드백</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허름한 샌드백</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rest_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stamina</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rest_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>찢어진 펀칭볼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cardio</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StandingOffense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개선되었지만 여전히 좁고 불편한 휴식 공간이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TrainingStaminaPerSecond</x:t>
-  </x:si>
-  <x:si>
     <x:t>세월의 흔적이 느껴지는 낡은 샌드백이다.</x:t>
   </x:si>
   <x:si>
     <x:t>때리면 터질 것 같은 허름한 샌드백이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>standing_offense</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -938,7 +941,7 @@
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="34.85546875" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="14.14453125" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="17.5703125" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="11.85546875" style="1" customWidth="1"/>
     <x:col min="4" max="5" width="34.85546875" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="14.5703125" style="1" customWidth="1"/>
@@ -951,148 +954,148 @@
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:18" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="P2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="Q2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="R2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18" s="6" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="M3" s="6" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N3" s="6" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H3" s="6" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I3" s="6" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J3" s="6" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K3" s="6" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="L3" s="6" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="M3" s="6" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="N3" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="O3" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="P3" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="Q3" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R3" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F4" s="1">
         <x:v>500</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J4" s="1">
         <x:v>10</x:v>
@@ -1124,31 +1127,31 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="3">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F5" s="1">
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J5" s="1">
         <x:v>15</x:v>
@@ -1180,16 +1183,16 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="4">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>53</x:v>
@@ -1198,13 +1201,13 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J6" s="4">
         <x:v>-5</x:v>
@@ -1236,16 +1239,16 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C7" s="4">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>52</x:v>
@@ -1254,13 +1257,13 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H7" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I7" s="1" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="H7" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="I7" s="1" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="J7" s="1">
         <x:v>-6</x:v>
@@ -1292,31 +1295,31 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="4">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>500</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J8" s="1">
         <x:v>-7</x:v>
@@ -1348,31 +1351,31 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C9" s="4">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>300</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J9" s="1">
         <x:v>-5</x:v>
